--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios184.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios184.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25929.30112390803</v>
+        <v>19930.89672919069</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29612.20924035081</v>
+        <v>21131.61949360075</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>17013.41770450048</v>
+        <v>9454.406136681617</v>
       </c>
     </row>
     <row r="9">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11064.29441335869</v>
+        <v>30710.17874968065</v>
       </c>
     </row>
     <row r="12">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2766.073603339673</v>
+        <v>7677.544687420163</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46310.06992466449</v>
+        <v>40737.70533379986</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14175.13854053429</v>
+        <v>12693.32081537286</v>
       </c>
     </row>
     <row r="18">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>29402.93150945902</v>
+        <v>23485.64799789194</v>
       </c>
     </row>
     <row r="21">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>25049.11493353405</v>
+        <v>26660.62796293196</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>14534.08988574538</v>
+        <v>10194.73644887774</v>
       </c>
     </row>
     <row r="27">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>15146.2166424452</v>
+        <v>18795.0965927501</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3786.5541606113</v>
+        <v>4698.774148187525</v>
       </c>
     </row>
     <row r="32">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>73368.58148477535</v>
+        <v>55909.28013490904</v>
       </c>
     </row>
     <row r="33">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16222.35538617286</v>
+        <v>9263.723232488781</v>
       </c>
     </row>
     <row r="36">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>14913.04159701121</v>
+        <v>33169.91017471116</v>
       </c>
     </row>
     <row r="39">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>16936.72713912433</v>
+        <v>33891.10389281224</v>
       </c>
     </row>
     <row r="42">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>8574.043437099102</v>
+        <v>14774.34734809527</v>
       </c>
     </row>
     <row r="45">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>24067.81982537917</v>
+        <v>20419.2583015789</v>
       </c>
     </row>
     <row r="48">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6016.954956344793</v>
+        <v>5104.814575394725</v>
       </c>
     </row>
     <row r="50">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>30729.08350373799</v>
+        <v>5140.978276931963</v>
       </c>
     </row>
     <row r="51">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>11258.6587467197</v>
+        <v>14091.09174745423</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>28410.28297312581</v>
+        <v>22065.02196078352</v>
       </c>
     </row>
     <row r="57">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>24503.75549090174</v>
+        <v>23152.94191436845</v>
       </c>
     </row>
     <row r="60">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>13470.82818392265</v>
+        <v>5384.835010539437</v>
       </c>
     </row>
     <row r="63">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>13605.18373190745</v>
+        <v>22961.53091524516</v>
       </c>
     </row>
     <row r="66">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3401.295932976863</v>
+        <v>5740.382728811289</v>
       </c>
     </row>
     <row r="68">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>58922.81560095867</v>
+        <v>28271.28429759568</v>
       </c>
     </row>
     <row r="69">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10200.45540321501</v>
+        <v>12944.09204746773</v>
       </c>
     </row>
     <row r="72">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>22565.35244201544</v>
+        <v>31784.93111432381</v>
       </c>
     </row>
     <row r="75">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>26782.9879592949</v>
+        <v>21480.03864011836</v>
       </c>
     </row>
     <row r="78">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>12886.54333074068</v>
+        <v>17060.19396960665</v>
       </c>
     </row>
     <row r="81">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>20143.88011409356</v>
+        <v>15518.05773075692</v>
       </c>
     </row>
     <row r="84">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5035.97002852339</v>
+        <v>3879.51443268923</v>
       </c>
     </row>
     <row r="86">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>38740.59767034867</v>
+        <v>59006.49615096502</v>
       </c>
     </row>
     <row r="87">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>11376.68970800303</v>
+        <v>7607.053432030522</v>
       </c>
     </row>
     <row r="90">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>25016.37693127777</v>
+        <v>32733.47826010393</v>
       </c>
     </row>
     <row r="93">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>14686.86075124686</v>
+        <v>31569.92786934467</v>
       </c>
     </row>
     <row r="96">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>10765.50137632483</v>
+        <v>14256.34221111399</v>
       </c>
     </row>
     <row r="99">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>22326.07927419708</v>
+        <v>17640.29518031713</v>
       </c>
     </row>
     <row r="102">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5581.51981854927</v>
+        <v>4410.073795079284</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>30838.45094231986</v>
+        <v>28969.99064857832</v>
       </c>
     </row>
     <row r="105">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>16837.1811934784</v>
+        <v>11035.09881792704</v>
       </c>
     </row>
     <row r="108">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>34522.09946949883</v>
+        <v>33327.30381811092</v>
       </c>
     </row>
     <row r="111">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>15661.37068029936</v>
+        <v>25974.71403676836</v>
       </c>
     </row>
     <row r="114">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>17591.07362393802</v>
+        <v>6676.111514328314</v>
       </c>
     </row>
     <row r="117">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>19138.5104677272</v>
+        <v>13251.63416348035</v>
       </c>
     </row>
     <row r="120">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4784.627616931799</v>
+        <v>3312.908540870088</v>
       </c>
     </row>
     <row r="122">
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>56277.71838735582</v>
+        <v>68797.27101278419</v>
       </c>
     </row>
     <row r="123">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>10637.55855451908</v>
+        <v>14329.67282047957</v>
       </c>
     </row>
     <row r="126">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>31922.83620420071</v>
+        <v>15744.99909445054</v>
       </c>
     </row>
     <row r="129">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>28045.705141365</v>
+        <v>11756.26377869055</v>
       </c>
     </row>
     <row r="132">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>9446.925287758986</v>
+        <v>10156.09199524975</v>
       </c>
     </row>
     <row r="135">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>13008.78800020827</v>
+        <v>8891.847752060485</v>
       </c>
     </row>
     <row r="138">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3252.197000052067</v>
+        <v>2222.961938015121</v>
       </c>
     </row>
     <row r="140">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>28095.46347186166</v>
+        <v>47662.48264989499</v>
       </c>
     </row>
     <row r="141">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>13204.78166162284</v>
+        <v>21693.59514438614</v>
       </c>
     </row>
     <row r="144">
